--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -39,12 +39,12 @@
     <t xml:space="preserve">Colchane</t>
   </si>
   <si>
+    <t xml:space="preserve">Huara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Huara</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pozo Almonte</t>
   </si>
   <si>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:41</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>90.95</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="3">
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>64.53</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>64.19</v>
+        <v>27.92</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51.55</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44.94</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>41.91</v>
+        <v>18.83</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37.4</v>
+        <v>15.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:08</t>
+    <t xml:space="preserve">2026-09-29 11:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>63.2</v>
+        <v>632.05</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.34</v>
+        <v>303.43</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.92</v>
+        <v>279.22</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24.13</v>
+        <v>241.3</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.1</v>
+        <v>201.03</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18.83</v>
+        <v>188.35</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.86</v>
+        <v>158.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:02</t>
+    <t xml:space="preserve">2026-10-01 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:27</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2023_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-05 07:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
